--- a/resources/openvas/OpenVAS_Metasploitable2.xlsx
+++ b/resources/openvas/OpenVAS_Metasploitable2.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,21 +497,6 @@
           <t>log_method</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>plugin_details</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>instances</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>plugin</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -544,7 +529,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>8787</v>
       </c>
@@ -603,17 +587,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -646,7 +619,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>80</v>
       </c>
@@ -688,17 +660,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -721,13 +682,11 @@
           <t>['Some of the information that can be gathered from this le includes: The username of the user running the PHP process, if it is a sudo user, the IP address of the host, the web server version, the system version (Unix, Linux, Windows, ...), and the root directory of the web server.']</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>80</v>
       </c>
@@ -769,17 +728,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -812,7 +760,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>80</v>
       </c>
@@ -854,17 +801,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -897,7 +833,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>80</v>
       </c>
@@ -939,17 +874,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -982,7 +906,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>80</v>
       </c>
@@ -1024,17 +947,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1057,13 +969,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>22</v>
       </c>
@@ -1105,17 +1015,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1138,13 +1037,11 @@
           <t>['Attackers can exploit this issue to execute arbitrary commands in the context of the application. Successful attacks will compromise the aected isystem.']</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>1524</v>
       </c>
@@ -1186,17 +1083,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1229,7 +1115,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>514</v>
       </c>
@@ -1271,17 +1156,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1314,7 +1188,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>21</v>
       </c>
@@ -1356,17 +1229,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1389,13 +1251,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>5432</v>
       </c>
@@ -1437,17 +1297,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1480,7 +1329,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>6667</v>
       </c>
@@ -1522,17 +1370,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1565,7 +1402,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>512</v>
       </c>
@@ -1607,17 +1443,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1640,13 +1465,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>3306</v>
       </c>
@@ -1688,17 +1511,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1731,7 +1543,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>6200</v>
       </c>
@@ -1773,17 +1584,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1816,7 +1616,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>513</v>
       </c>
@@ -1858,17 +1657,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1901,7 +1689,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>general</t>
@@ -1945,17 +1732,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1988,7 +1764,6 @@
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>3632</v>
       </c>
@@ -2030,17 +1805,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2063,13 +1827,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>5900</v>
       </c>
@@ -2111,17 +1873,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2154,7 +1905,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>80</v>
       </c>
@@ -2196,17 +1946,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2239,7 +1978,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>80</v>
       </c>
@@ -2281,17 +2019,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2324,7 +2051,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>80</v>
       </c>
@@ -2366,17 +2092,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2409,7 +2124,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>80</v>
       </c>
@@ -2451,17 +2165,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2494,7 +2197,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>80</v>
       </c>
@@ -2536,17 +2238,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2579,7 +2270,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>80</v>
       </c>
@@ -2621,17 +2311,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2664,7 +2343,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>80</v>
       </c>
@@ -2706,17 +2384,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2751,7 +2418,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>80</v>
       </c>
@@ -2793,17 +2459,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2836,7 +2491,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>80</v>
       </c>
@@ -2878,17 +2532,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2921,7 +2564,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>80</v>
       </c>
@@ -2963,17 +2605,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3006,7 +2637,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>80</v>
       </c>
@@ -3048,17 +2678,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3091,7 +2710,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>80</v>
       </c>
@@ -3133,17 +2751,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3176,7 +2783,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>80</v>
       </c>
@@ -3218,17 +2824,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3261,7 +2856,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>22</v>
       </c>
@@ -3303,17 +2897,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3336,13 +2919,11 @@
           <t>['An attacker can uncover login names and passwords by sniffing traffic to the FTP service.']</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>21</v>
       </c>
@@ -3384,17 +2965,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3427,7 +2997,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>445</v>
       </c>
@@ -3469,17 +3038,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3512,7 +3070,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>21</v>
       </c>
@@ -3556,17 +3113,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3589,13 +3135,11 @@
           <t>['An attacker can uncover login names and passwords by sning trac to the FTP service.']</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2121</v>
       </c>
@@ -3637,17 +3181,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3680,7 +3213,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>25</v>
       </c>
@@ -3722,17 +3254,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3755,13 +3276,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>25</v>
       </c>
@@ -3803,17 +3322,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3846,7 +3354,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>25</v>
       </c>
@@ -3888,17 +3395,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3931,7 +3427,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>25</v>
       </c>
@@ -3973,17 +3468,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4016,7 +3500,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>25</v>
       </c>
@@ -4058,17 +3541,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4101,7 +3573,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>25</v>
       </c>
@@ -4143,17 +3614,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4186,7 +3646,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>25</v>
       </c>
@@ -4228,17 +3687,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4271,7 +3719,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>5432</v>
       </c>
@@ -4315,17 +3762,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4358,7 +3794,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>5432</v>
       </c>
@@ -4400,17 +3835,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4443,7 +3867,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>5432</v>
       </c>
@@ -4488,17 +3911,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4521,13 +3933,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>5432</v>
       </c>
@@ -4569,17 +3979,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4612,7 +4011,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>5432</v>
       </c>
@@ -4654,17 +4052,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4697,7 +4084,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>5432</v>
       </c>
@@ -4739,17 +4125,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4782,7 +4157,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>5432</v>
       </c>
@@ -4824,17 +4198,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4867,7 +4230,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>25</v>
       </c>
@@ -4912,17 +4274,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4955,7 +4306,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>6667</v>
       </c>
@@ -5001,17 +4351,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5034,13 +4373,11 @@
           <t>['An attacker can uncover login names and passwords by sning trac to the Telnet service.']</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>23</v>
       </c>
@@ -5082,17 +4419,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5125,7 +4451,6 @@
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>5900</v>
       </c>
@@ -5169,17 +4494,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5212,7 +4526,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>80</v>
       </c>
@@ -5258,17 +4571,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5291,13 +4593,11 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>22</v>
       </c>
@@ -5340,17 +4640,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5383,7 +4672,6 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>general</t>
@@ -5431,17 +4719,6 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/openvas/OpenVAS_Metasploitable2.xlsx
+++ b/resources/openvas/OpenVAS_Metasploitable2.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['Successful exploitation could allow execution of arbitrary script code or commands. This could let attackers steal cookie-based authentication credentials or compromise the aected application.']</t>
+          <t>['Successful exploitation could allow execution of arbitrary script code or commands. This could let attackers steal cookie-based authentication credentials or compromise the affected application.']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['Exploiting this issue allows remote attackers to view the source code of les in the context of the server process. This may allow the attacker to obtain sensitive information and to run arbitrary PHP code on the aected computer. Other attacks are also possible.']</t>
+          <t>['Exploiting this issue allows remote attackers to view the source code of les in the context of the server process. This may allow the attacker to obtain sensitive information and to run arbitrary PHP code on the affected computer. Other attacks are also possible.']</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>['Miscongured web servers allows remote clients to perform dangerous HTTP methods such as PUT and DELETE. This script checks if they are enabled and can be misused to upload or delete les.']</t>
+          <t>['Misconfigured web servers allows remote clients to perform dangerous HTTP methods such as PUT and DELETE. This script checks if they are enabled and can be misused to upload or delete les.']</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>['Attackers can exploit this issue to execute arbitrary commands in the context of the application. Successful attacks will compromise the aected isystem.']</t>
+          <t>['Attackers can exploit this issue to execute arbitrary commands in the context of the application. Successful attacks will compromise the affected isystem.']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>['Attackers can exploit this issue to execute arbitrary commands in the context of the application. Successful attacks will compromise the aected application.']</t>
+          <t>['Attackers can exploit this issue to execute arbitrary commands in the context of the application. Successful attacks will compromise the affected application.']</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['Remote attackers can exploit this issue to execute arbitrary system commands within the context of the aected application.', 'The issue aects Unreal 3.2.8.1 for Linux. Reportedly package Unreal3.2.8.1.tar.gz downloaded in November 2009 and later is aected. The MD5 sum of the aected le is 752e46f2d873c1679fa99de3f52a274d. Files with MD5 sum of 7b741e94e867c0a7370553fd01506c66 are not aected.']</t>
+          <t>['Remote attackers can exploit this issue to execute arbitrary system commands within the context of the affected application.', 'The issue affects Unreal 3.2.8.1 for Linux. Reportedly package Unreal3.2.8.1.tar.gz downloaded in November 2009 and later is affected. The MD5 sum of the affected le is 752e46f2d873c1679fa99de3f52a274d. Files with MD5 sum of 7b741e94e867c0a7370553fd01506c66 are not affected.']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['rexec (Remote Process Execution) has the same kind of functionality that rsh has: you can execute shell commands on a remote computer.', 'The main dierence is that rexec authenticate by reading the username and password *unencrypted* from the socket.']</t>
+          <t>['rexec (Remote Process Execution) has the same kind of functionality that rsh has: you can execute shell commands on a remote computer.', 'The main difference is that rexec authenticate by reading the username and password *unencrypted* from the socket.']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>['Attackers can exploit this issue to execute arbitrary commands in the context of the application. Successful attacks will compromise the aected application.']</t>
+          <t>['Attackers can exploit this issue to execute arbitrary commands in the context of the application. Successful attacks will compromise the affected application.']</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['DistCC 2.x, as used in XCode 1.5 and others, when not congured to restrict access to the server port, allows remote attackers to execute arbitrary commands via compilation jobs, which are executed by the server without authorization checks.']</t>
+          <t>['DistCC 2.x, as used in XCode 1.5 and others, when not configured to restrict access to the server port, allows remote attackers to execute arbitrary commands via compilation jobs, which are executed by the server without authorization checks.']</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['Solution type: Mitigation', 'Disable the TRACE and TRACK methods in your web server conguration.', 'Please see the manual of your web server or the references for more information.']</t>
+          <t>['Solution type: Mitigation', 'Disable the TRACE and TRACK methods in your web server configuration.', 'Please see the manual of your web server or the references for more information.']</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>['Successful exploitation could allow arbitrary code execution in the context of an aected site.']</t>
+          <t>['Successful exploitation could allow arbitrary code execution in the context of an affected site.']</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>['An attacker can uncover login names and passwords by sning trac to the FTP service.']</t>
+          <t>['An attacker can uncover login names and passwords by sniffing traffic to the FTP service.']</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[""The remote server's SSL/TLS certicate has already expired.""]</t>
+          <t>[""The remote server's SSL/TLS certificate has already expired.""]</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['Replace the SSL/TLS certicate by a new one.']</t>
+          <t>['Replace the SSL/TLS certificate by a new one.']</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>['Disable VRFY and/or EXPN on your Mailserver.', ""For postx add 'disable_vrfy_command=yes' in 'main.cf'."", ""For Sendmail add the option 'O PrivacyOptions=goaway'."", 'It is suggested that, if you really want to publish this type of information, you use a mechanism that legitimate users actually know about, such as Finger or HTTP.']</t>
+          <t>['Disable VRFY and/or EXPN on your Mailserver.', ""For postfix add 'disable_vrfy_command=yes' in 'main.cf'."", ""For Sendmail add the option 'O PrivacyOptions=goaway'."", 'It is suggested that, if you really want to publish this type of information, you use a mechanism that legitimate users actually know about, such as Finger or HTTP.']</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>['Successful exploitation will allow a man-in-the-middle attacker to downgrade the security of a TLS session to 512-bit export-grade cryptography, which is signicantly weaker, allowing the attacker to more easily break the encryption and monitor or tamper with the encrypted stream.']</t>
+          <t>['Successful exploitation will allow a man-in-the-middle attacker to downgrade the security of a TLS session to 512-bit export-grade cryptography, which is significantly weaker, allowing the attacker to more easily break the encryption and monitor or tamper with the encrypted stream.']</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>[""Flaw is triggered when handling Die-Hellman key exchanges dened in the 'DHE_EXPORT' cipher suites.""]</t>
+          <t>[""Flaw is triggered when handling Diffie-Hellman key exchanges defined in the 'DHE_EXPORT' cipher suites.""]</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[""Successful exploitation will allow remote attacker to downgrade the security of a session to use 'RSA_EXPORT' cipher suites, which are signicantly weaker than non-export cipher suites. This may allow a man-in-the-middle attacker to more easily break the encryption and monitor or tamper with the encrypted stream.""]</t>
+          <t>[""Successful exploitation will allow remote attacker to downgrade the security of a session to use 'RSA_EXPORT' cipher suites, which are significantly weaker than non-export cipher suites. This may allow a man-in-the-middle attacker to more easily break the encryption and monitor or tamper with the encrypted stream.""]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>['The remote service is using a SSL/TLS certicate in the certicate chain that has been signed using a cryptographically weak hashing algorithm.']</t>
+          <t>['The remote service is using a SSL/TLS certificate in the certificate chain that has been signed using a cryptographically weak hashing algorithm.']</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>['Servers that use SSL/TLS certicates signed with a weak SHA-1, MD5, MD4 or MD2 hashing algorithm will need to obtain new SHA-2 signed SSL/TLS certicates to avoid web browser SSL/TLS certicate warnings.']</t>
+          <t>['Servers that use SSL/TLS certificates signed with a weak SHA-1, MD5, MD4 or MD2 hashing algorithm will need to obtain new SHA-2 signed SSL/TLS certificates to avoid web browser SSL/TLS certificate warnings.']</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>['The following hashing algorithms used for signing SSL/TLS certicates are considered cryptographically weak and not secure enough for ongoing use:', '- Secure Hash Algorithm 1 (SHA-1)', '- Message Digest 5 (MD5)', '- Message Digest 4 (MD4)', '- Message Digest 2 (MD2)', 'Beginning as late as January 2017 and as early as June 2016, browser developers such as Microsoft and Google will begin warning users when visiting web sites that use SHA-1 signed Secure Socket Layer (SSL) certicates.', 'NOTE: The script preference allows to set one or more custom SHA-1 ngerprints of CA certicates which are trusted by this routine. The ngerprints needs to be passed comma-separated and case-insensitive: Fingerprint1 or ngerprint1,Fingerprint2']</t>
+          <t>['The following hashing algorithms used for signing SSL/TLS certificates are considered cryptographically weak and not secure enough for ongoing use:', '- Secure Hash Algorithm 1 (SHA-1)', '- Message Digest 5 (MD5)', '- Message Digest 4 (MD4)', '- Message Digest 2 (MD2)', 'Beginning as late as January 2017 and as early as June 2016, browser developers such as Microsoft and Google will begin warning users when visiting web sites that use SHA-1 signed Secure Socket Layer (SSL) certificates.', 'NOTE: The script preference allows to set one or more custom SHA-1 ngerprints of CA certificates which are trusted by this routine. The ngerprints needs to be passed comma-separated and case-insensitive: Fingerprint1 or ngerprint1,Fingerprint2']</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>['Check which hashing algorithm was used to sign the remote SSL/TLS certicate Details: SSL/TLS: Certificate Signed Using A Weak Signature Algorithm
+          <t>['Check which hashing algorithm was used to sign the remote SSL/TLS certificate Details: SSL/TLS: Certificate Signed Using A Weak Signature Algorithm
 OID:1.3.6.1.4.1.25623.1.0.105880
 Version used: $Revision: 11524 $.']</t>
         </is>
@@ -3771,17 +3771,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>['The SSL/TLS service uses Die-Hellman groups with insucient strength (key size &lt; 2048).']</t>
+          <t>['The SSL/TLS service uses Diffie-Hellman groups with insufficient strength (key size &lt; 2048).']</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>['Deploy (Ephemeral) Elliptic-Curve Die-Hellman (ECDHE) or use a 2048-bit or stronger Die-Hellman group (see the references). For Apache Web Servers: Beginning with version 2.4.7, mod_ssl will use DH parameters which include primes with lengths of more than 1024 bits.']</t>
+          <t>['Deploy (Ephemeral) Elliptic-Curve Diffie-Hellman (ECDHE) or use a 2048-bit or stronger Diffie-Hellman group (see the references). For Apache Web Servers: Beginning with version 2.4.7, mod_ssl will use DH parameters which include primes with lengths of more than 1024 bits.']</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>['An attacker might be able to decrypt the SSL/TLS communication _x001F_offline.']</t>
+          <t>['An attacker might be able to decrypt the SSL/TLS communication offline.']</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>['The Die-Hellman group are some big numbers that are used as base for the DH computations. They can be, and often are, xed. The security of the nal secret depends on the size of these parameters. It was found that 512 and 768 bits to be weak, 1024 bits to be breakable by really powerful attackers like governments.']</t>
+          <t>['The Diffie-Hellman group are some big numbers that are used as base for the DH computations. They can be, and often are, xed. The security of the nal secret depends on the size of these parameters. It was found that 512 and 768 bits to be weak, 1024 bits to be breakable by really powerful attackers like governments.']</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3920,12 +3920,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[""The remote server's SSL/TLS certicate has already expired.""]</t>
+          <t>[""The remote server's SSL/TLS certificate has already expired.""]</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>['Replace the SSL/TLS certicate by a new one.']</t>
+          <t>['Replace the SSL/TLS certificate by a new one.']</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>['This routine reports all Weak SSL/TLS cipher suites accepted by a service.', ""NOTE: No severity for SMTP services with 'Opportunistic TLS' and weak cipher suites on port 25/tcp is reported. If too strong cipher suites are congured for this service the alternative would be to fall back to an even more insecure cleartext communication.""]</t>
+          <t>['This routine reports all Weak SSL/TLS cipher suites accepted by a service.', ""NOTE: No severity for SMTP services with 'Opportunistic TLS' and weak cipher suites on port 25/tcp is reported. If too strong cipher suites are configured for this service the alternative would be to fall back to an even more insecure cleartext communication.""]</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>['The conguration of this services should be changed so that it does not accept the listed weak cipher suites anymore. Please see the references for more resources supporting you with this task.']</t>
+          <t>['The configuration of this services should be changed so that it does not accept the listed weak cipher suites anymore. Please see the references for more resources supporting you with this task.']</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>['The SSL/TLS service uses Di_x001E_e-Hellman groups with insu_x001E_cient strength (key size &lt; 2048).']</t>
+          <t>['The SSL/TLS service uses Diffie-Hellman groups with insufficient strength (key size &lt; 2048).']</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>['This host is installed with UnrealIRCd and is prone to authentication spoong vulnerability.']</t>
+          <t>['This host is installed with UnrealIRCd and is prone to authentication spoofing vulnerability.']</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>['Successful exploitation of this vulnerability will allows remote attackers to spoof certicate n-gerprints and consequently log in as another user.']</t>
+          <t>['Successful exploitation of this vulnerability will allows remote attackers to spoof certificate n-gerprints and consequently log in as another user.']</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>['An attacker can uncover login names and passwords by sning trac to the Telnet service.']</t>
+          <t>['An attacker can uncover login names and passwords by sniffing traffic to the Telnet service.']</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>['An attacker can uncover sensitive data by sning trac to the VNC server.']</t>
+          <t>['An attacker can uncover sensitive data by sniffing traffic to the VNC server.']</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>['The remote SSH server is congured to allow weak MD5 and/or 96-bit MAC algorithms.']</t>
+          <t>['The remote SSH server is configured to allow weak MD5 and/or 96-bit MAC algorithms.']</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>['A side eect of this feature is that the uptime of the remote host can sometimes be computed.']</t>
+          <t>['A side effect of this feature is that the uptime of the remote host can sometimes be computed.']</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>['The remote host implements TCP timestamps, as dened by RFC1323.']</t>
+          <t>['The remote host implements TCP timestamps, as defined by RFC1323.']</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">

--- a/resources/openvas/OpenVAS_Metasploitable2.xlsx
+++ b/resources/openvas/OpenVAS_Metasploitable2.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -529,6 +529,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>8787</v>
       </c>
@@ -619,6 +620,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>80</v>
       </c>
@@ -682,11 +684,13 @@
           <t>['Some of the information that can be gathered from this le includes: The username of the user running the PHP process, if it is a sudo user, the IP address of the host, the web server version, the system version (Unix, Linux, Windows, ...), and the root directory of the web server.']</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>80</v>
       </c>
@@ -760,6 +764,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>80</v>
       </c>
@@ -833,6 +838,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>80</v>
       </c>
@@ -906,6 +912,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>80</v>
       </c>
@@ -969,11 +976,13 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>22</v>
       </c>
@@ -1037,11 +1046,13 @@
           <t>['Attackers can exploit this issue to execute arbitrary commands in the context of the application. Successful attacks will compromise the affected isystem.']</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>1524</v>
       </c>
@@ -1115,6 +1126,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>514</v>
       </c>
@@ -1188,6 +1200,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>21</v>
       </c>
@@ -1251,11 +1264,13 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>5432</v>
       </c>
@@ -1329,6 +1344,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>6667</v>
       </c>
@@ -1402,6 +1418,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>512</v>
       </c>
@@ -1465,11 +1482,13 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>3306</v>
       </c>
@@ -1543,6 +1562,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>6200</v>
       </c>
@@ -1616,6 +1636,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>513</v>
       </c>
@@ -1689,6 +1710,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>general</t>
@@ -1764,6 +1786,7 @@
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>3632</v>
       </c>
@@ -1827,11 +1850,13 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>5900</v>
       </c>
@@ -1905,6 +1930,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>80</v>
       </c>
@@ -1978,6 +2004,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>80</v>
       </c>
@@ -2051,6 +2078,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>80</v>
       </c>
@@ -2124,6 +2152,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>80</v>
       </c>
@@ -2197,6 +2226,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>80</v>
       </c>
@@ -2270,6 +2300,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>80</v>
       </c>
@@ -2343,6 +2374,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>80</v>
       </c>
@@ -2418,6 +2450,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>80</v>
       </c>
@@ -2491,6 +2524,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>80</v>
       </c>
@@ -2564,6 +2598,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>80</v>
       </c>
@@ -2637,6 +2672,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>80</v>
       </c>
@@ -2710,6 +2746,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>80</v>
       </c>
@@ -2783,6 +2820,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>80</v>
       </c>
@@ -2856,6 +2894,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>22</v>
       </c>
@@ -2919,11 +2958,13 @@
           <t>['An attacker can uncover login names and passwords by sniffing traffic to the FTP service.']</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>21</v>
       </c>
@@ -2997,6 +3038,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>445</v>
       </c>
@@ -3070,6 +3112,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>21</v>
       </c>
@@ -3135,11 +3178,13 @@
           <t>['An attacker can uncover login names and passwords by sniffing traffic to the FTP service.']</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2121</v>
       </c>
@@ -3213,6 +3258,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>25</v>
       </c>
@@ -3276,11 +3322,13 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>25</v>
       </c>
@@ -3304,7 +3352,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>['The certificate of the remote service expired on 2010-04-16 14:07:45.', 'Certificate details: subject ...: 1.2.840.113549.1.9.1=#726F6F74407562756E74753830342D626173652E6C6F63616C646F6D61696E,CN=ubuntu804-base.localdomain,OU=Office for Complication of Otherwise Simple Affairs,O=OCOSA,L=Everywhere,ST=There is no such thing outside US,C=XX', 'subject alternative names (SAN): None', 'issued by .: 1.2.840.113549.1.9.1=#726F6F74407562756E74753830342D626173652E6C6F63616C646F6D61696E,CN=ubuntu804-base.localdomain,OU=Office for Complication of Otherwise Simple Affairs,O=OCOSA,L=Everywhere,ST=There is no such thing outside US,C=XX', 'serial ....: 00FAF93A4C7FB6B9CC', 'valid from : 2010-03-17 14:07:45 UTC', 'valid until: 2010-04-16 14:07:45 UTC', 'fingerprint (SHA-1): ED093088706603BFD5DC237399B498DA2D4D31C6', 'fingerprint (SHA-256): E7A7FA0D63E457C7C4A59B38B70849C6A70BDA6F830C7AF1E32DEE436DE813CC']</t>
+          <t>['The certificate of the remote service expired on 2010-04-16 14:07:45.', 'Certificate details: subject ...: 1.2.840.113549.1.9.1=#726F6F74407562756E74753830342D626173652E6C6F63616C646F6D61696E,CN=ubuntu804-base.localdomain,OU=Office for Complication of Otherwise Simple Affairs,O=OCOSA,L=Everywhere,ST=There is no such thing outside US,C=XX', 'subject alternative names (SAN): None', 'issued by .: 1.2.840.113549.1.9.1=#726F6F74407562756E74753830342D626173652E6C6F63616C646F6D61696E,CN=ubuntu804-base.localdomain,OU=Office for Complication of Otherwise Simple Affairs,O=OCOSA,L=Everywhere,ST=There is no such thing outside US,C=XX', 'serial ....: 00FAF93A4C7FB6B9CC', 'valid from : 2010-03-17 14:07:45 UTC', 'valid until: 2010-04-16 14:07:45 UTC', 'fingerprint (SHA-1): ED093088706603BFD5DC237399B498DA2D4D31C6']</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3354,6 +3402,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>25</v>
       </c>
@@ -3427,6 +3476,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>25</v>
       </c>
@@ -3500,6 +3550,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>25</v>
       </c>
@@ -3573,6 +3624,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>25</v>
       </c>
@@ -3646,6 +3698,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>25</v>
       </c>
@@ -3719,6 +3772,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>5432</v>
       </c>
@@ -3794,6 +3848,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>5432</v>
       </c>
@@ -3867,6 +3922,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>5432</v>
       </c>
@@ -3933,11 +3989,13 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>5432</v>
       </c>
@@ -4011,6 +4069,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>5432</v>
       </c>
@@ -4084,6 +4143,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>5432</v>
       </c>
@@ -4157,6 +4217,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>5432</v>
       </c>
@@ -4230,6 +4291,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>25</v>
       </c>
@@ -4306,6 +4368,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>6667</v>
       </c>
@@ -4373,11 +4436,13 @@
           <t>['An attacker can uncover login names and passwords by sniffing traffic to the Telnet service.']</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>23</v>
       </c>
@@ -4451,6 +4516,7 @@
           <t>MEDIUM</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>5900</v>
       </c>
@@ -4526,6 +4592,7 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>80</v>
       </c>
@@ -4593,11 +4660,13 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>22</v>
       </c>
@@ -4672,6 +4741,7 @@
           <t>LOW</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>general</t>
